--- a/tests/fixtures/lom/102728-1-LOM.xlsx
+++ b/tests/fixtures/lom/102728-1-LOM.xlsx
@@ -14,35 +14,20 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>QTY</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>ITEM</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>PART NO</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ITEM</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>PART NO</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
@@ -51,1887 +36,1122 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>102727-5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>102728-1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PLATE A</t>
+          <t>TUBE, ROUND</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>102727-4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>102728-2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PLATE B</t>
+          <t>TUBE, ROUND</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>102727-3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>102728-3</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PLATE C</t>
+          <t>TUBE, ROUND</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>102727-2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>102728-4</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PLATE D</t>
+          <t>TUBE, ROUND</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>102727-1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>102728-5</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PLATE E</t>
+          <t>TUBE, ROUND</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>102726-1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>102728-6</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PLATE F</t>
+          <t>HOOK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AW</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>102725-1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>102728-7</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PLATE G</t>
+          <t>PLATE, FRONT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>102712-1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>102728-8</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>PLATE H</t>
+          <t>CABLE ENCLOSURE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>102711-1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>102728-9</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>PLATE J</t>
+          <t>CABLE TUBE WELDMENT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100366-27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>102728-10</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>PLATE K</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100267-1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>102728-11</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>PLATE L</t>
+          <t>CONTROL BOX PLATFORM MT.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33688-10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>102728-12</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>PLATE M</t>
+          <t>EXPANDED METAL PLATE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AQ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33688-9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>102728-13</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>PLATE N</t>
+          <t>EXPANDED METAL PLATE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33688-8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>102728-14</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>PLATE P</t>
+          <t>EXPANDED METAL PLATE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33688-7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>102728-15</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>PLATE Q</t>
+          <t>EXPANDED METAL PLATE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33688-6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>102728-16</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>PLATE R</t>
+          <t>EXPANDED METAL PLATE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100738-1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>102728-17</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>PLATE S</t>
+          <t>RAIL, VERTICAL MIDDLE FRONT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100351-3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>102728-18</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>PLATE T</t>
+          <t>RECTANGLE TUBE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AJ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100351-2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>102728-19</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>PLATE U</t>
+          <t>RECTANGLE TUBE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100373-1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>102728-20</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>PLATE V</t>
+          <t>TUBE, GRATING SUPPORT SIDES</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100350-2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>102728-21</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>PLATE W</t>
+          <t>TUBE, GRATING SUPPORT MIDDLE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AF</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>464460</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>102728-22</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>PLATE X</t>
+          <t>RAIL, HORIZONTAL FRONT OUTER</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>436010</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>102728-23</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>PLATE Y</t>
+          <t>RAIL, SIDE TOP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>464440</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>102728-24</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>PLATE Z</t>
+          <t>PLATE, SUPPORT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100177-2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>102728-25</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>PLATE A1</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>464450</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>102728-26</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>PLATE B1</t>
+          <t>RAIL TOP FRONT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>460330</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>102728-27</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>PLATE C1</t>
+          <t>CAP, VERTICAL RAIL BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>460320</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>102728-28</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>PLATE D1</t>
+          <t>CAP, VERTICAL RAIL TOP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100363-1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>102728-29</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>PLATE E1</t>
+          <t>ANGLE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>432670</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>102728-30</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>PLATE F1</t>
+          <t>RAIL, HORIZONTAL BACK OUTER</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>432690</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>102728-31</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>PLATE G1</t>
+          <t>RAIL, CORNER VERTICAL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>432710</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>102728-32</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>PLATE H1</t>
+          <t>CAP, 2 x 1 TUBE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>298540</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>102728-33</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>PLATE J1</t>
+          <t>CAP, TUBE RAIL</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>464100</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>102728-34</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>PLATE K1</t>
+          <t>PIN, PLATFORM SHOCK</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>94560</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>102728-35</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>PLATE L1</t>
+          <t>GATE, FABRICATION</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>432660</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>102728-36</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>PLATE M1</t>
+          <t>RAIL, BACK TOP</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>432650</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>N1</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>102728-37</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>PLATE N1</t>
+          <t>RAIL, HORIZONTAL CENTER BACK</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100362-1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>102728-38</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>PLATE P1</t>
+          <t>ROUND TUBE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>460340</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>102728-39</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>PLATE Q1</t>
+          <t>TUBE, TOP RAIL</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>460300</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>102728-40</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>PLATE R1</t>
+          <t>RAIL, BOTTOM RIGHT HAND</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>460230</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>102728-41</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>PLATE S1</t>
+          <t>RAIL, VERTICAL MIDDLE FRONT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>432640</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>102728-42</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>PLATE T1</t>
+          <t>RAIL, VERTICAL MIDDLE BACK</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>102733-1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>102728-43</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>PLATE U1</t>
+          <t>GRATING</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100351-1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>102728-44</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>PLATE V1</t>
+          <t>RECTANGLE TUBE</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100373-2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>102728-45</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>PLATE W1</t>
+          <t>TUBE, GRATING SUPPORT SIDES</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100350-1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>X1</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>102728-46</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>PLATE X1</t>
+          <t>TUBE, GRATING SUPPORT MIDDLE</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>432600</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>102728-47</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>PLATE Y1</t>
+          <t>RAIL, BOTTOM SIDE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>432580</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>102728-48</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>PLATE Z1</t>
+          <t>RAIL, BOTTOM BACK</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>460280</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>102728-49</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>PLATE A2</t>
+          <t>RAIL, BOTTOM FRONT LEFT HAND</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>460270</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>102728-50</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>PLATE B2</t>
+          <t>RAIL, BOTTOM FRONT RIGHT HAND</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>460200</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>102728-51</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>PLATE C2</t>
+          <t>RAIL, BOTTOM FRONT MIDDLE</t>
         </is>
       </c>
     </row>
@@ -1972,83 +1192,83 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>102728-1</t>
+          <t>102727-5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PLATE A</t>
+          <t>TUBE, ROUND</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>102728-2</t>
+          <t>102727-4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PLATE B</t>
+          <t>TUBE, ROUND</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>102728-3</t>
+          <t>102727-3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PLATE C</t>
+          <t>TUBE, ROUND</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>102728-4</t>
+          <t>102727-2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PLATE D</t>
+          <t>TUBE, ROUND</t>
         </is>
       </c>
     </row>
@@ -2060,17 +1280,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>102728-5</t>
+          <t>102727-1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PLATE E</t>
+          <t>TUBE, ROUND</t>
         </is>
       </c>
     </row>
@@ -2082,83 +1302,83 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>AX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>102728-6</t>
+          <t>102726-1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PLATE F</t>
+          <t>HOOK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>AW</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>102728-7</t>
+          <t>102725-1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PLATE G</t>
+          <t>PLATE, FRONT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>AV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>102728-8</t>
+          <t>102712-1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PLATE H</t>
+          <t>CABLE ENCLOSURE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>102728-9</t>
+          <t>102711-1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PLATE J</t>
+          <t>CABLE TUBE WELDMENT</t>
         </is>
       </c>
     </row>
@@ -2170,61 +1390,61 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>102728-10</t>
+          <t>100366-27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PLATE K</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>102728-11</t>
+          <t>100267-1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PLATE L</t>
+          <t>CONTROL BOX PLATFORM MT.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>102728-12</t>
+          <t>33688-10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PLATE M</t>
+          <t>EXPANDED METAL PLATE</t>
         </is>
       </c>
     </row>
@@ -2236,17 +1456,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>AQ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>102728-13</t>
+          <t>33688-9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PLATE N</t>
+          <t>EXPANDED METAL PLATE</t>
         </is>
       </c>
     </row>
@@ -2258,17 +1478,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>102728-14</t>
+          <t>33688-8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PLATE P</t>
+          <t>EXPANDED METAL PLATE</t>
         </is>
       </c>
     </row>
@@ -2280,105 +1500,105 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>AN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>102728-15</t>
+          <t>33688-7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PLATE Q</t>
+          <t>EXPANDED METAL PLATE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>102728-16</t>
+          <t>33688-6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PLATE R</t>
+          <t>EXPANDED METAL PLATE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>102728-17</t>
+          <t>100738-1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PLATE S</t>
+          <t>RAIL, VERTICAL MIDDLE FRONT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>AK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>102728-18</t>
+          <t>100351-3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PLATE T</t>
+          <t>RECTANGLE TUBE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>AJ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>102728-19</t>
+          <t>100351-2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PLATE U</t>
+          <t>RECTANGLE TUBE</t>
         </is>
       </c>
     </row>
@@ -2390,39 +1610,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>AH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>102728-20</t>
+          <t>100373-1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PLATE V</t>
+          <t>TUBE, GRATING SUPPORT SIDES</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>AG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>102728-21</t>
+          <t>100350-2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PLATE W</t>
+          <t>TUBE, GRATING SUPPORT MIDDLE</t>
         </is>
       </c>
     </row>
@@ -2434,17 +1654,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>AF</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>102728-22</t>
+          <t>464460</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PLATE X</t>
+          <t>RAIL, HORIZONTAL FRONT OUTER</t>
         </is>
       </c>
     </row>
@@ -2456,105 +1676,105 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>102728-23</t>
+          <t>436010</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PLATE Y</t>
+          <t>RAIL, SIDE TOP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>102728-24</t>
+          <t>464440</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PLATE Z</t>
+          <t>PLATE, SUPPORT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>102728-25</t>
+          <t>100177-2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PLATE A1</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>102728-26</t>
+          <t>464450</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PLATE B1</t>
+          <t>RAIL TOP FRONT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>102728-27</t>
+          <t>460330</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PLATE C1</t>
+          <t>CAP, VERTICAL RAIL BOTTOM</t>
         </is>
       </c>
     </row>
@@ -2566,39 +1786,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>102728-28</t>
+          <t>460320</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PLATE D1</t>
+          <t>CAP, VERTICAL RAIL TOP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>102728-29</t>
+          <t>100363-1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PLATE E1</t>
+          <t>ANGLE</t>
         </is>
       </c>
     </row>
@@ -2610,61 +1830,61 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>102728-30</t>
+          <t>432670</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PLATE F1</t>
+          <t>RAIL, HORIZONTAL BACK OUTER</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>102728-31</t>
+          <t>432690</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PLATE G1</t>
+          <t>RAIL, CORNER VERTICAL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>102728-32</t>
+          <t>432710</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PLATE H1</t>
+          <t>CAP, 2 x 1 TUBE</t>
         </is>
       </c>
     </row>
@@ -2676,17 +1896,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>102728-33</t>
+          <t>298540</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PLATE J1</t>
+          <t>CAP, TUBE RAIL</t>
         </is>
       </c>
     </row>
@@ -2698,17 +1918,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>102728-34</t>
+          <t>464100</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PLATE K1</t>
+          <t>PIN, PLATFORM SHOCK</t>
         </is>
       </c>
     </row>
@@ -2720,61 +1940,61 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>102728-35</t>
+          <t>94560</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PLATE L1</t>
+          <t>GATE, FABRICATION</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>102728-36</t>
+          <t>432660</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PLATE M1</t>
+          <t>RAIL, BACK TOP</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>102728-37</t>
+          <t>432650</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PLATE N1</t>
+          <t>RAIL, HORIZONTAL CENTER BACK</t>
         </is>
       </c>
     </row>
@@ -2786,39 +2006,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>102728-38</t>
+          <t>100362-1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PLATE P1</t>
+          <t>ROUND TUBE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>102728-39</t>
+          <t>460340</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PLATE Q1</t>
+          <t>TUBE, TOP RAIL</t>
         </is>
       </c>
     </row>
@@ -2830,39 +2050,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>102728-40</t>
+          <t>460300</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PLATE R1</t>
+          <t>RAIL, BOTTOM RIGHT HAND</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>102728-41</t>
+          <t>460230</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PLATE S1</t>
+          <t>RAIL, VERTICAL MIDDLE FRONT</t>
         </is>
       </c>
     </row>
@@ -2874,61 +2094,61 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>102728-42</t>
+          <t>432640</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PLATE T1</t>
+          <t>RAIL, VERTICAL MIDDLE BACK</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>102728-43</t>
+          <t>102733-1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PLATE U1</t>
+          <t>GRATING</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>102728-44</t>
+          <t>100351-1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PLATE V1</t>
+          <t>RECTANGLE TUBE</t>
         </is>
       </c>
     </row>
@@ -2940,39 +2160,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>102728-45</t>
+          <t>100373-2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PLATE W1</t>
+          <t>TUBE, GRATING SUPPORT SIDES</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>102728-46</t>
+          <t>100350-1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PLATE X1</t>
+          <t>TUBE, GRATING SUPPORT MIDDLE</t>
         </is>
       </c>
     </row>
@@ -2984,105 +2204,105 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Y1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>102728-47</t>
+          <t>432600</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PLATE Y1</t>
+          <t>RAIL, BOTTOM SIDE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Z1</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>102728-48</t>
+          <t>432580</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PLATE Z1</t>
+          <t>RAIL, BOTTOM BACK</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>102728-49</t>
+          <t>460280</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PLATE A2</t>
+          <t>RAIL, BOTTOM FRONT LEFT HAND</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>102728-50</t>
+          <t>460270</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PLATE B2</t>
+          <t>RAIL, BOTTOM FRONT RIGHT HAND</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>102728-51</t>
+          <t>460200</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PLATE C2</t>
+          <t>RAIL, BOTTOM FRONT MIDDLE</t>
         </is>
       </c>
     </row>
